--- a/SGC-CKN/Excel/76f618a7-2ef0-4ca9-95e5-796de72fc8ca_Thanh_Hoá_P1-111_D800_03-04-2026.xlsx
+++ b/SGC-CKN/Excel/76f618a7-2ef0-4ca9-95e5-796de72fc8ca_Thanh_Hoá_P1-111_D800_03-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="69">
   <si>
     <t>Dự án</t>
   </si>
@@ -157,26 +157,22 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">23:31
+    <t xml:space="preserve">24:00
 02/04/2026</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+  </si>
+  <si>
     <t xml:space="preserve">01:00
-02/04/2026</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01:01
-02/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">02:00
-02/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -186,11 +182,11 @@
   </si>
   <si>
     <t xml:space="preserve">02:01
-02/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">03:02
-02/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t>Chạm sỏi</t>
@@ -203,11 +199,11 @@
   </si>
   <si>
     <t xml:space="preserve">03:05
-02/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">05:23
-02/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -1298,16 +1294,16 @@
         <v>-8.3</v>
       </c>
       <c r="G14" s="17">
-        <v>-18.2</v>
+        <v>-17.2</v>
       </c>
       <c r="H14" s="17">
         <v>0.98</v>
       </c>
       <c r="I14" s="17">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
       <c r="J14" s="12">
-        <v>10.07</v>
+        <v>9.05</v>
       </c>
       <c r="K14" s="18" t="s">
         <v>30</v>
@@ -1324,25 +1320,25 @@
         <v>44</v>
       </c>
       <c r="D15" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="22" t="s">
-        <v>46</v>
-      </c>
       <c r="F15" s="20">
-        <v>-18.2</v>
+        <v>-17.2</v>
       </c>
       <c r="G15" s="20">
         <v>-22.5</v>
       </c>
       <c r="H15" s="20">
-        <v>1.48</v>
+        <v>0.5</v>
       </c>
       <c r="I15" s="20">
-        <v>4.3</v>
-      </c>
-      <c r="J15" s="16">
-        <v>2.9</v>
+        <v>5.3</v>
+      </c>
+      <c r="J15" s="12">
+        <v>10.6</v>
       </c>
       <c r="K15" s="21" t="s">
         <v>30</v>
@@ -1350,19 +1346,19 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="E16" s="25" t="s">
         <v>49</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>50</v>
       </c>
       <c r="F16" s="23">
         <v>-22.5</v>
@@ -1371,13 +1367,13 @@
         <v>-27.4</v>
       </c>
       <c r="H16" s="23">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="I16" s="23">
         <v>4.9</v>
       </c>
       <c r="J16" s="16">
-        <v>4.98</v>
+        <v>4.9</v>
       </c>
       <c r="K16" s="24" t="s">
         <v>30</v>
@@ -1385,57 +1381,57 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17" s="26" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="E17" s="28" t="s">
         <v>53</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>54</v>
       </c>
       <c r="F17" s="26">
         <v>-27.4</v>
       </c>
       <c r="G17" s="26">
-        <v>-33.2</v>
+        <v>-39.2</v>
       </c>
       <c r="H17" s="26">
         <v>1.02</v>
       </c>
       <c r="I17" s="26">
-        <v>5.8</v>
+        <v>11.8</v>
       </c>
       <c r="J17" s="12">
-        <v>5.7</v>
+        <v>11.61</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="E18" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="31" t="s">
-        <v>59</v>
-      </c>
       <c r="F18" s="29">
-        <v>-33.2</v>
+        <v>-39.2</v>
       </c>
       <c r="G18" s="29">
         <v>-44.36</v>
@@ -1444,10 +1440,10 @@
         <v>2.3</v>
       </c>
       <c r="I18" s="29">
-        <v>11.16</v>
+        <v>5.16</v>
       </c>
       <c r="J18" s="16">
-        <v>4.85</v>
+        <v>2.24</v>
       </c>
       <c r="K18" s="30" t="s">
         <v>30</v>
@@ -1455,7 +1451,7 @@
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
@@ -1561,31 +1557,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1692,16 +1688,16 @@
         <v>-8.3</v>
       </c>
       <c r="F5" s="17">
-        <v>-18.2</v>
+        <v>-17.2</v>
       </c>
       <c r="G5" s="17">
         <v>0.98</v>
       </c>
       <c r="H5" s="17">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
       <c r="I5" s="12">
-        <v>10.07</v>
+        <v>9.05</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1718,19 +1714,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="20">
-        <v>-18.2</v>
+        <v>-17.2</v>
       </c>
       <c r="F6" s="20">
         <v>-22.5</v>
       </c>
       <c r="G6" s="20">
-        <v>1.48</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="20">
-        <v>4.3</v>
-      </c>
-      <c r="I6" s="16">
-        <v>2.9</v>
+        <v>5.3</v>
+      </c>
+      <c r="I6" s="12">
+        <v>10.6</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1741,7 +1737,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="23">
         <v>1</v>
@@ -1753,13 +1749,13 @@
         <v>-27.4</v>
       </c>
       <c r="G7" s="23">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H7" s="23">
         <v>4.9</v>
       </c>
       <c r="I7" s="16">
-        <v>4.98</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1770,7 +1766,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8" s="26">
         <v>1</v>
@@ -1779,16 +1775,16 @@
         <v>-27.4</v>
       </c>
       <c r="F8" s="26">
-        <v>-33.2</v>
+        <v>-39.2</v>
       </c>
       <c r="G8" s="26">
         <v>1.02</v>
       </c>
       <c r="H8" s="26">
-        <v>5.8</v>
+        <v>11.8</v>
       </c>
       <c r="I8" s="12">
-        <v>5.7</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1799,13 +1795,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9" s="29">
         <v>1</v>
       </c>
       <c r="E9" s="29">
-        <v>-33.2</v>
+        <v>-39.2</v>
       </c>
       <c r="F9" s="29">
         <v>-44.36</v>
@@ -1814,15 +1810,15 @@
         <v>2.3</v>
       </c>
       <c r="H9" s="29">
-        <v>11.16</v>
+        <v>5.16</v>
       </c>
       <c r="I9" s="16">
-        <v>4.85</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>30</v>
@@ -1840,13 +1836,13 @@
         <v>-44.36</v>
       </c>
       <c r="G10" s="34">
-        <v>19.07</v>
+        <v>18.1</v>
       </c>
       <c r="H10" s="34">
         <v>44.36</v>
       </c>
       <c r="I10" s="34">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
     </row>
   </sheetData>
